--- a/data/merged/2026-09-23/MERGED_JP_Robot-Vacuum_2026-09-23.xlsx
+++ b/data/merged/2026-09-23/MERGED_JP_Robot-Vacuum_2026-09-23.xlsx
@@ -5462,50 +5462,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId49" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5847,7 +5803,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -11250,7 +11206,7 @@
       <c r="B49" s="11"/>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>B0H6J7R2MX</t>
+          <t>B0H7JNCWDQ</t>
         </is>
       </c>
       <c r="D49" s="12"/>
@@ -11263,23 +11219,23 @@
       </c>
       <c r="H49" s="12" t="inlineStr">
         <is>
-          <t>ECOVACS ECOVACS 清洁剂 WINBOT 机器人吸尘器用 消耗品 专用清洗剂1升(1瓶)WINBOT MINI/W2s适用于WINBOT MINI2/W2 OMNI</t>
+          <t>dreame KARA 10s Roller AE机器人吸尘器+DREAME地板洗涤剂</t>
         </is>
       </c>
       <c r="I49" s="12"/>
       <c r="J49" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0H6J7R2MX?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0H7JNCWDQ?psc=1</t>
         </is>
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/31KewPWnvYL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/31fXNapZykL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L49" s="12" t="inlineStr">
         <is>
-          <t>B0H6J7R2MX</t>
+          <t>B0H7JNCWDQ</t>
         </is>
       </c>
       <c r="M49" s="1"/>
@@ -11352,7 +11308,7 @@
       <c r="B50" s="11"/>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>B0H7JNCWDQ</t>
+          <t>B0H9RVW5X7</t>
         </is>
       </c>
       <c r="D50" s="12"/>
@@ -11365,23 +11321,23 @@
       </c>
       <c r="H50" s="12" t="inlineStr">
         <is>
-          <t>dreame KARA 10s Roller AE机器人吸尘器+DREAME地板洗涤剂</t>
+          <t>ECOVACS WINBOT W2S PRO OMNI 窗户擦拭机器人 自动清洁 窗户用 多功能站 超声波喷雾器s防坠落系统/自动电缆存储/映射/避障/谷歌/Alexa兼容/制造商保修长达 2 年</t>
         </is>
       </c>
       <c r="I50" s="12"/>
       <c r="J50" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0H7JNCWDQ?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0H9RVW5X7?psc=1</t>
         </is>
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/31fXNapZykL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/41EO2r2gVRL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L50" s="12" t="inlineStr">
         <is>
-          <t>B0H7JNCWDQ</t>
+          <t>B0H9RVW5X7</t>
         </is>
       </c>
       <c r="M50" s="1"/>
@@ -11401,9 +11357,13 @@
       <c r="AA50"/>
       <c r="AB50"/>
       <c r="AC50"/>
-      <c r="AD50" s="17"/>
+      <c r="AD50" s="17">
+        <v>398</v>
+      </c>
       <c r="AE50"/>
-      <c r="AF50" s="18"/>
+      <c r="AF50" s="18">
+        <v>4.2</v>
+      </c>
       <c r="AG50" s="19">
         <v>0</v>
       </c>
@@ -11446,112 +11406,6 @@
       <c r="BP50"/>
       <c r="BQ50" s="20"/>
       <c r="BR50"/>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="11">
-        <v>50</v>
-      </c>
-      <c r="B51" s="11"/>
-      <c r="C51" s="12" t="inlineStr">
-        <is>
-          <t>B0H9RVW5X7</t>
-        </is>
-      </c>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51"/>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>ECOVACS WINBOT W2S PRO OMNI 窗户擦拭机器人 自动清洁 窗户用 多功能站 超声波喷雾器s防坠落系统/自动电缆存储/映射/避障/谷歌/Alexa兼容/制造商保修长达 2 年</t>
-        </is>
-      </c>
-      <c r="I51" s="12"/>
-      <c r="J51" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0H9RVW5X7?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/41EO2r2gVRL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="12" t="inlineStr">
-        <is>
-          <t>B0H9RVW5X7</t>
-        </is>
-      </c>
-      <c r="M51" s="1"/>
-      <c r="N51" s="12"/>
-      <c r="O51" s="13"/>
-      <c r="P51" s="13"/>
-      <c r="Q51" s="14"/>
-      <c r="R51" s="15"/>
-      <c r="S51" s="16"/>
-      <c r="T51" s="13"/>
-      <c r="U51" s="14"/>
-      <c r="V51" s="13"/>
-      <c r="W51" s="13"/>
-      <c r="X51" s="13"/>
-      <c r="Y51"/>
-      <c r="Z51" s="2"/>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51"/>
-      <c r="AD51" s="17">
-        <v>398</v>
-      </c>
-      <c r="AE51"/>
-      <c r="AF51" s="18">
-        <v>4.2</v>
-      </c>
-      <c r="AG51" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH51"/>
-      <c r="AI51" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="1"/>
-      <c r="AL51" s="17"/>
-      <c r="AM51"/>
-      <c r="AN51" s="11"/>
-      <c r="AO51" s="11"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="17"/>
-      <c r="AR51"/>
-      <c r="AS51"/>
-      <c r="AT51"/>
-      <c r="AU51" s="11"/>
-      <c r="AV51" s="12"/>
-      <c r="AW51" s="11"/>
-      <c r="AX51" s="11"/>
-      <c r="AY51" s="11"/>
-      <c r="AZ51" s="11"/>
-      <c r="BA51" s="11"/>
-      <c r="BB51" s="11"/>
-      <c r="BC51" s="11"/>
-      <c r="BD51" s="11"/>
-      <c r="BE51" s="11"/>
-      <c r="BF51" s="11"/>
-      <c r="BG51" s="11"/>
-      <c r="BH51" s="12"/>
-      <c r="BI51"/>
-      <c r="BJ51"/>
-      <c r="BK51" s="20"/>
-      <c r="BL51"/>
-      <c r="BM51" s="20"/>
-      <c r="BN51"/>
-      <c r="BO51" s="20"/>
-      <c r="BP51"/>
-      <c r="BQ51" s="20"/>
-      <c r="BR51"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11792,23 +11646,18 @@
     <hyperlink ref="J48" r:id="rId233" tooltip="https://www.amazon.co.jp/dp/B0H44Y871S?psc=1"/>
     <hyperlink ref="K48" r:id="rId234" tooltip="https://images-fe.ssl-images-amazon.com/images/I/619JkwsWdlL._AC_UL300_SR300,200_.jpg"/>
     <hyperlink ref="L48" r:id="rId235" tooltip="https://www.amazon.co.jp/dp/B0H44Y871S"/>
-    <hyperlink ref="C49" r:id="rId236" tooltip="https://www.amazon.co.jp/dp/B0H6J7R2MX"/>
+    <hyperlink ref="C49" r:id="rId236" tooltip="https://www.amazon.co.jp/dp/B0H7JNCWDQ"/>
     <hyperlink ref="G49" r:id="rId237" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J49" r:id="rId238" tooltip="https://www.amazon.co.jp/dp/B0H6J7R2MX?psc=1"/>
-    <hyperlink ref="K49" r:id="rId239" tooltip="https://images-fe.ssl-images-amazon.com/images/I/31KewPWnvYL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L49" r:id="rId240" tooltip="https://www.amazon.co.jp/dp/B0H6J7R2MX"/>
-    <hyperlink ref="C50" r:id="rId241" tooltip="https://www.amazon.co.jp/dp/B0H7JNCWDQ"/>
+    <hyperlink ref="J49" r:id="rId238" tooltip="https://www.amazon.co.jp/dp/B0H7JNCWDQ?psc=1"/>
+    <hyperlink ref="K49" r:id="rId239" tooltip="https://images-fe.ssl-images-amazon.com/images/I/31fXNapZykL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L49" r:id="rId240" tooltip="https://www.amazon.co.jp/dp/B0H7JNCWDQ"/>
+    <hyperlink ref="C50" r:id="rId241" tooltip="https://www.amazon.co.jp/dp/B0H9RVW5X7"/>
     <hyperlink ref="G50" r:id="rId242" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J50" r:id="rId243" tooltip="https://www.amazon.co.jp/dp/B0H7JNCWDQ?psc=1"/>
-    <hyperlink ref="K50" r:id="rId244" tooltip="https://images-fe.ssl-images-amazon.com/images/I/31fXNapZykL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L50" r:id="rId245" tooltip="https://www.amazon.co.jp/dp/B0H7JNCWDQ"/>
-    <hyperlink ref="C51" r:id="rId246" tooltip="https://www.amazon.co.jp/dp/B0H9RVW5X7"/>
-    <hyperlink ref="G51" r:id="rId247" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J51" r:id="rId248" tooltip="https://www.amazon.co.jp/dp/B0H9RVW5X7?psc=1"/>
-    <hyperlink ref="K51" r:id="rId249" tooltip="https://images-fe.ssl-images-amazon.com/images/I/41EO2r2gVRL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId250" tooltip="https://www.amazon.co.jp/dp/B0H9RVW5X7"/>
+    <hyperlink ref="J50" r:id="rId243" tooltip="https://www.amazon.co.jp/dp/B0H9RVW5X7?psc=1"/>
+    <hyperlink ref="K50" r:id="rId244" tooltip="https://images-fe.ssl-images-amazon.com/images/I/41EO2r2gVRL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L50" r:id="rId245" tooltip="https://www.amazon.co.jp/dp/B0H9RVW5X7"/>
   </hyperlinks>
-  <drawing r:id="rId251"/>
+  <drawing r:id="rId246"/>
 </worksheet>
 </file>
 
